--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_PICKEN CLARET.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_PICKEN CLARET.xlsx
@@ -565,13 +565,13 @@
         <v>25</v>
       </c>
       <c r="D2" t="n">
-        <v>45.458</v>
+        <v>29.6891</v>
       </c>
       <c r="E2" t="n">
-        <v>63.0422</v>
+        <v>48.1946</v>
       </c>
       <c r="F2" t="n">
-        <v>-17.5844</v>
+        <v>-18.5058</v>
       </c>
       <c r="G2" t="n">
         <v>25.238</v>
@@ -610,13 +610,13 @@
         <v>46.364</v>
       </c>
       <c r="S2" t="n">
-        <v>26.9624</v>
+        <v>11.1934</v>
       </c>
       <c r="T2" t="n">
-        <v>23.8189</v>
+        <v>8.9716</v>
       </c>
       <c r="U2" t="n">
-        <v>3.1434</v>
+        <v>2.2217</v>
       </c>
       <c r="V2" t="n">
         <v>-18.2878</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. ALVAREZ LABRADOR</t>
+          <t>L. ALBEROLA GUILLOT</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>22</v>
       </c>
       <c r="D5" t="n">
-        <v>11.8843</v>
+        <v>3.9814</v>
       </c>
       <c r="E5" t="n">
-        <v>24.9233</v>
+        <v>3.4228</v>
       </c>
       <c r="F5" t="n">
-        <v>-13.0391</v>
+        <v>0.5588</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.909899999999999</v>
+        <v>-26.709</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.9316</v>
+        <v>-23.5294</v>
       </c>
       <c r="I5" t="n">
-        <v>1.0216</v>
+        <v>-3.179599999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>28.8009</v>
+        <v>14.0095</v>
       </c>
       <c r="K5" t="n">
-        <v>21.7171</v>
+        <v>10.3552</v>
       </c>
       <c r="L5" t="n">
-        <v>7.083699999999999</v>
+        <v>3.654400000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>-30.7112</v>
+        <v>-40.7184</v>
       </c>
       <c r="N5" t="n">
-        <v>-24.649</v>
+        <v>-33.8845</v>
       </c>
       <c r="O5" t="n">
-        <v>-6.0623</v>
+        <v>-6.834000000000001</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1833000000000005</v>
+        <v>-7.1471</v>
       </c>
       <c r="Q5" t="n">
-        <v>-35.5521</v>
+        <v>-56.2601</v>
       </c>
       <c r="R5" t="n">
-        <v>35.7354</v>
+        <v>49.1131</v>
       </c>
       <c r="S5" t="n">
-        <v>15.0111</v>
+        <v>4.8049</v>
       </c>
       <c r="T5" t="n">
-        <v>12.5864</v>
+        <v>1.7549</v>
       </c>
       <c r="U5" t="n">
-        <v>2.4247</v>
+        <v>3.0499</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.3999</v>
+        <v>33.033</v>
       </c>
       <c r="W5" t="n">
-        <v>19.0878</v>
+        <v>43.9187</v>
       </c>
       <c r="X5" t="n">
-        <v>-20.4876</v>
+        <v>-10.8857</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. LARIO ECHEVARRIAS</t>
+          <t>P. ALVAREZ LABRADOR</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.0124</v>
+        <v>3.7318</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5149000000000001</v>
+        <v>17.6441</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.5273</v>
+        <v>-13.9122</v>
       </c>
       <c r="G6" t="n">
-        <v>-6.796399999999999</v>
+        <v>-1.909899999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>-5.3601</v>
+        <v>-2.9316</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.4364</v>
+        <v>1.0216</v>
       </c>
       <c r="J6" t="n">
-        <v>2.5297</v>
+        <v>28.8009</v>
       </c>
       <c r="K6" t="n">
-        <v>1.4326</v>
+        <v>21.7171</v>
       </c>
       <c r="L6" t="n">
-        <v>1.0972</v>
+        <v>7.083699999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>-9.3262</v>
+        <v>-30.7112</v>
       </c>
       <c r="N6" t="n">
-        <v>-6.7925</v>
+        <v>-24.649</v>
       </c>
       <c r="O6" t="n">
-        <v>-2.5334</v>
+        <v>-6.0623</v>
       </c>
       <c r="P6" t="n">
-        <v>4.764699999999999</v>
+        <v>0.1833000000000005</v>
       </c>
       <c r="Q6" t="n">
-        <v>-4.7648</v>
+        <v>-35.5521</v>
       </c>
       <c r="R6" t="n">
-        <v>9.529399999999999</v>
+        <v>35.7354</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5196999999999999</v>
+        <v>6.8586</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1371000000000001</v>
+        <v>5.3074</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3826000000000001</v>
+        <v>1.5518</v>
       </c>
       <c r="V6" t="n">
-        <v>1.5391</v>
+        <v>-1.3999</v>
       </c>
       <c r="W6" t="n">
-        <v>2.8871</v>
+        <v>19.0878</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.348</v>
+        <v>-20.4876</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R. ARNAL GARCIA</t>
+          <t>P. LARIO ECHEVARRIAS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.0296</v>
+        <v>0.5717999999999996</v>
       </c>
       <c r="E7" t="n">
-        <v>0.989</v>
+        <v>1.1608</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.0186</v>
+        <v>-0.5890999999999997</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.1842</v>
+        <v>-6.796399999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0595</v>
+        <v>-5.3601</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2437</v>
+        <v>-1.4364</v>
       </c>
       <c r="J7" t="n">
-        <v>1.3012</v>
+        <v>2.5297</v>
       </c>
       <c r="K7" t="n">
-        <v>0.5511</v>
+        <v>1.4326</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7501</v>
+        <v>1.0972</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.4854</v>
+        <v>-9.3262</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.4916</v>
+        <v>-6.7925</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.9938</v>
+        <v>-2.5334</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9163</v>
+        <v>4.764699999999999</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-4.7648</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9163</v>
+        <v>9.529399999999999</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4947</v>
+        <v>1.0646</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3122</v>
+        <v>0.5089</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1825</v>
+        <v>0.5558</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.267</v>
+        <v>1.5391</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2.8871</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.267</v>
+        <v>-1.348</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>L. ALBEROLA GUILLOT</t>
+          <t>R. ARNAL GARCIA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,70 +1030,70 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.867500000000001</v>
+        <v>-0.5488</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.750099999999999</v>
+        <v>1.4698</v>
       </c>
       <c r="F8" t="n">
-        <v>1.8824</v>
+        <v>-2.0186</v>
       </c>
       <c r="G8" t="n">
-        <v>-26.709</v>
+        <v>-0.1842</v>
       </c>
       <c r="H8" t="n">
-        <v>-23.5294</v>
+        <v>0.0595</v>
       </c>
       <c r="I8" t="n">
-        <v>-3.179599999999999</v>
+        <v>-0.2437</v>
       </c>
       <c r="J8" t="n">
-        <v>14.0095</v>
+        <v>1.3012</v>
       </c>
       <c r="K8" t="n">
-        <v>10.3552</v>
+        <v>0.5511</v>
       </c>
       <c r="L8" t="n">
-        <v>3.654400000000001</v>
+        <v>0.7501</v>
       </c>
       <c r="M8" t="n">
-        <v>-40.7184</v>
+        <v>-1.4854</v>
       </c>
       <c r="N8" t="n">
-        <v>-33.8845</v>
+        <v>-0.4916</v>
       </c>
       <c r="O8" t="n">
-        <v>-6.834000000000001</v>
+        <v>-0.9938</v>
       </c>
       <c r="P8" t="n">
-        <v>-7.1471</v>
+        <v>0.9163</v>
       </c>
       <c r="Q8" t="n">
-        <v>-56.2601</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>49.1131</v>
+        <v>0.9163</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.0445</v>
+        <v>-0.0139</v>
       </c>
       <c r="T8" t="n">
-        <v>-5.4179</v>
+        <v>0.1686</v>
       </c>
       <c r="U8" t="n">
-        <v>4.3736</v>
+        <v>-0.1825</v>
       </c>
       <c r="V8" t="n">
-        <v>33.033</v>
+        <v>-1.267</v>
       </c>
       <c r="W8" t="n">
-        <v>43.9187</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-10.8857</v>
+        <v>-1.267</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>16</v>
       </c>
       <c r="D9" t="n">
-        <v>-6.6649</v>
+        <v>-3.6849</v>
       </c>
       <c r="E9" t="n">
-        <v>5.042800000000001</v>
+        <v>7.4198</v>
       </c>
       <c r="F9" t="n">
-        <v>-11.7077</v>
+        <v>-11.1046</v>
       </c>
       <c r="G9" t="n">
         <v>-2.1412</v>
@@ -1156,13 +1156,13 @@
         <v>8.246599999999999</v>
       </c>
       <c r="S9" t="n">
-        <v>-3.9113</v>
+        <v>-0.9314</v>
       </c>
       <c r="T9" t="n">
-        <v>-2.0968</v>
+        <v>0.2801999999999999</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.815</v>
+        <v>-1.2115</v>
       </c>
       <c r="V9" t="n">
         <v>-3.1779</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. ALMELA LOPEZ</t>
+          <t>M. SHALABI TORRES</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="D10" t="n">
-        <v>-14.9666</v>
+        <v>-11.4212</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.8644</v>
+        <v>11.3241</v>
       </c>
       <c r="F10" t="n">
-        <v>-9.1022</v>
+        <v>-22.7454</v>
       </c>
       <c r="G10" t="n">
-        <v>-8.022600000000001</v>
+        <v>-13.8737</v>
       </c>
       <c r="H10" t="n">
-        <v>-4.5512</v>
+        <v>-18.7471</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.4714</v>
+        <v>4.873099999999999</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.7424</v>
+        <v>30.8387</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.1307</v>
+        <v>19.6438</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.6117</v>
+        <v>11.1952</v>
       </c>
       <c r="M10" t="n">
-        <v>-6.2803</v>
+        <v>-44.7124</v>
       </c>
       <c r="N10" t="n">
-        <v>-4.4204</v>
+        <v>-38.3905</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.8597</v>
+        <v>-6.322</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.6492</v>
+        <v>23.0904</v>
       </c>
       <c r="Q10" t="n">
-        <v>-5.4978</v>
+        <v>-33.3531</v>
       </c>
       <c r="R10" t="n">
-        <v>3.8483</v>
+        <v>56.4433</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.7503</v>
+        <v>-4.568000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.1583</v>
+        <v>1.4485</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.592</v>
+        <v>-6.0167</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.5444</v>
+        <v>-16.0697</v>
       </c>
       <c r="W10" t="n">
-        <v>2.534</v>
+        <v>12.3896</v>
       </c>
       <c r="X10" t="n">
-        <v>-5.0783</v>
+        <v>-28.4593</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. SHALABI TORRES</t>
+          <t>M. ALMELA LOPEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,70 +1264,70 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>-27.8091</v>
+        <v>-14.2558</v>
       </c>
       <c r="E11" t="n">
-        <v>2.421600000000001</v>
+        <v>-5.9055</v>
       </c>
       <c r="F11" t="n">
-        <v>-30.2307</v>
+        <v>-8.350299999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>-13.8737</v>
+        <v>-8.022600000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>-18.7471</v>
+        <v>-4.5512</v>
       </c>
       <c r="I11" t="n">
-        <v>4.873099999999999</v>
+        <v>-3.4714</v>
       </c>
       <c r="J11" t="n">
-        <v>30.8387</v>
+        <v>-1.7424</v>
       </c>
       <c r="K11" t="n">
-        <v>19.6438</v>
+        <v>-0.1307</v>
       </c>
       <c r="L11" t="n">
-        <v>11.1952</v>
+        <v>-1.6117</v>
       </c>
       <c r="M11" t="n">
-        <v>-44.7124</v>
+        <v>-6.2803</v>
       </c>
       <c r="N11" t="n">
-        <v>-38.3905</v>
+        <v>-4.4204</v>
       </c>
       <c r="O11" t="n">
-        <v>-6.322</v>
+        <v>-1.8597</v>
       </c>
       <c r="P11" t="n">
-        <v>23.0904</v>
+        <v>-1.6492</v>
       </c>
       <c r="Q11" t="n">
-        <v>-33.3531</v>
+        <v>-5.4978</v>
       </c>
       <c r="R11" t="n">
-        <v>56.4433</v>
+        <v>3.8483</v>
       </c>
       <c r="S11" t="n">
-        <v>-20.9557</v>
+        <v>-2.0396</v>
       </c>
       <c r="T11" t="n">
-        <v>-7.4541</v>
+        <v>-1.1994</v>
       </c>
       <c r="U11" t="n">
-        <v>-13.5019</v>
+        <v>-0.8402000000000001</v>
       </c>
       <c r="V11" t="n">
-        <v>-16.0697</v>
+        <v>-2.5444</v>
       </c>
       <c r="W11" t="n">
-        <v>12.3896</v>
+        <v>2.534</v>
       </c>
       <c r="X11" t="n">
-        <v>-28.4593</v>
+        <v>-5.0783</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>25</v>
       </c>
       <c r="D12" t="n">
-        <v>-28.7137</v>
+        <v>-30.7566</v>
       </c>
       <c r="E12" t="n">
-        <v>-9.7941</v>
+        <v>-12.7182</v>
       </c>
       <c r="F12" t="n">
-        <v>-18.9199</v>
+        <v>-18.0384</v>
       </c>
       <c r="G12" t="n">
         <v>-26.1796</v>
@@ -1390,13 +1390,13 @@
         <v>32.4365</v>
       </c>
       <c r="S12" t="n">
-        <v>0.6012000000000001</v>
+        <v>-1.4417</v>
       </c>
       <c r="T12" t="n">
-        <v>3.3194</v>
+        <v>0.3951000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>-2.7182</v>
+        <v>-1.837</v>
       </c>
       <c r="V12" t="n">
         <v>-11.3821</v>
@@ -1423,13 +1423,13 @@
         <v>22</v>
       </c>
       <c r="D13" t="n">
-        <v>-43.6399</v>
+        <v>-44.0335</v>
       </c>
       <c r="E13" t="n">
-        <v>-24.1686</v>
+        <v>-24.5928</v>
       </c>
       <c r="F13" t="n">
-        <v>-19.4712</v>
+        <v>-19.4408</v>
       </c>
       <c r="G13" t="n">
         <v>-23.8497</v>
@@ -1468,13 +1468,13 @@
         <v>27.1221</v>
       </c>
       <c r="S13" t="n">
-        <v>2.3503</v>
+        <v>1.9565</v>
       </c>
       <c r="T13" t="n">
-        <v>2.1112</v>
+        <v>1.6871</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2388999999999998</v>
+        <v>0.2695</v>
       </c>
       <c r="V13" t="n">
         <v>-11.8778</v>
@@ -1501,13 +1501,13 @@
         <v>23</v>
       </c>
       <c r="D14" t="n">
-        <v>-51.0555</v>
+        <v>-51.8801</v>
       </c>
       <c r="E14" t="n">
-        <v>-24.3095</v>
+        <v>-23.3606</v>
       </c>
       <c r="F14" t="n">
-        <v>-26.7461</v>
+        <v>-28.5201</v>
       </c>
       <c r="G14" t="n">
         <v>-33.701</v>
@@ -1546,13 +1546,13 @@
         <v>29.8708</v>
       </c>
       <c r="S14" t="n">
-        <v>0.8674999999999997</v>
+        <v>0.04279999999999995</v>
       </c>
       <c r="T14" t="n">
-        <v>1.2491</v>
+        <v>2.1984</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3819</v>
+        <v>-2.1556</v>
       </c>
       <c r="V14" t="n">
         <v>-25.919</v>
@@ -1579,13 +1579,13 @@
         <v>24</v>
       </c>
       <c r="D15" t="n">
-        <v>-66.2996</v>
+        <v>-57.5441</v>
       </c>
       <c r="E15" t="n">
-        <v>-37.4642</v>
+        <v>-32.2573</v>
       </c>
       <c r="F15" t="n">
-        <v>-28.8353</v>
+        <v>-25.2873</v>
       </c>
       <c r="G15" t="n">
         <v>-43.9687</v>
@@ -1624,13 +1624,13 @@
         <v>33.3528</v>
       </c>
       <c r="S15" t="n">
-        <v>-12.6483</v>
+        <v>-3.8931</v>
       </c>
       <c r="T15" t="n">
-        <v>-4.5396</v>
+        <v>0.6673999999999999</v>
       </c>
       <c r="U15" t="n">
-        <v>-8.108499999999999</v>
+        <v>-4.5606</v>
       </c>
       <c r="V15" t="n">
         <v>-1.0695</v>
@@ -1657,13 +1657,13 @@
         <v>26</v>
       </c>
       <c r="D16" t="n">
-        <v>-67.7803</v>
+        <v>-59.8004</v>
       </c>
       <c r="E16" t="n">
-        <v>-36.0062</v>
+        <v>-31.5135</v>
       </c>
       <c r="F16" t="n">
-        <v>-31.7737</v>
+        <v>-28.287</v>
       </c>
       <c r="G16" t="n">
         <v>-37.7366</v>
@@ -1702,13 +1702,13 @@
         <v>38.4843</v>
       </c>
       <c r="S16" t="n">
-        <v>-11.4243</v>
+        <v>-3.4446</v>
       </c>
       <c r="T16" t="n">
-        <v>-3.5951</v>
+        <v>0.8972999999999999</v>
       </c>
       <c r="U16" t="n">
-        <v>-7.8295</v>
+        <v>-4.3422</v>
       </c>
       <c r="V16" t="n">
         <v>-16.7863</v>
@@ -1735,13 +1735,13 @@
         <v>25</v>
       </c>
       <c r="D17" t="n">
-        <v>-77.0226</v>
+        <v>-71.3562</v>
       </c>
       <c r="E17" t="n">
-        <v>-51.2651</v>
+        <v>-48.1734</v>
       </c>
       <c r="F17" t="n">
-        <v>-25.7572</v>
+        <v>-23.1824</v>
       </c>
       <c r="G17" t="n">
         <v>-63.5537</v>
@@ -1780,13 +1780,13 @@
         <v>45.631</v>
       </c>
       <c r="S17" t="n">
-        <v>-6.4544</v>
+        <v>-0.7882000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.639</v>
+        <v>1.4525</v>
       </c>
       <c r="U17" t="n">
-        <v>-4.8157</v>
+        <v>-2.2408</v>
       </c>
       <c r="V17" t="n">
         <v>-18.9258</v>
@@ -1813,13 +1813,13 @@
         <v>26</v>
       </c>
       <c r="D18" t="n">
-        <v>-77.7698</v>
+        <v>-76.4228</v>
       </c>
       <c r="E18" t="n">
-        <v>-52.332</v>
+        <v>-51.6025</v>
       </c>
       <c r="F18" t="n">
-        <v>-25.4376</v>
+        <v>-24.8204</v>
       </c>
       <c r="G18" t="n">
         <v>-23.5946</v>
@@ -1858,13 +1858,13 @@
         <v>43.7985</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3274999999999996</v>
+        <v>1.0194</v>
       </c>
       <c r="T18" t="n">
-        <v>0.9326999999999999</v>
+        <v>1.6622</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.2605</v>
+        <v>-0.6428</v>
       </c>
       <c r="V18" t="n">
         <v>-17.9288</v>
@@ -1891,13 +1891,13 @@
         <v>26</v>
       </c>
       <c r="D19" t="n">
-        <v>-364.328</v>
+        <v>-339.7691</v>
       </c>
       <c r="E19" t="n">
-        <v>-104.0592</v>
+        <v>-95.5266</v>
       </c>
       <c r="F19" t="n">
-        <v>-260.2686</v>
+        <v>-244.2436</v>
       </c>
       <c r="G19" t="n">
         <v>-243.0217</v>
@@ -1921,10 +1921,10 @@
         <v>-427.1219</v>
       </c>
       <c r="N19" t="n">
-        <v>-328.815</v>
+        <v>-328.8150000000001</v>
       </c>
       <c r="O19" t="n">
-        <v>-98.3065</v>
+        <v>-98.30650000000001</v>
       </c>
       <c r="P19" t="n">
         <v>5.497300000000003</v>
@@ -1936,13 +1936,13 @@
         <v>460.8924</v>
       </c>
       <c r="S19" t="n">
-        <v>-14.7382</v>
+        <v>9.819700000000001</v>
       </c>
       <c r="T19" t="n">
-        <v>17.6676</v>
+        <v>26.2007</v>
       </c>
       <c r="U19" t="n">
-        <v>-32.4077</v>
+        <v>-16.3812</v>
       </c>
       <c r="V19" t="n">
         <v>-112.0639</v>
